--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101442</v>
+        <v>101445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101445</v>
+        <v>101446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101446</v>
+        <v>101451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11014-2026 artfynd.xlsx
+++ b/artfynd/A 11014-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136532482</v>
       </c>
       <c r="B2" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136548511</v>
       </c>
       <c r="B3" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136533736</v>
       </c>
       <c r="B4" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
